--- a/data/xlsx/krs.xlsx
+++ b/data/xlsx/krs.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="krs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KRS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'krs'!$A$1:$M$91</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -45,7 +43,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,18 +51,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,6123 +423,8132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="39" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>numerKRS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>nip</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>regon</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nazwa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nazwaSkrocona</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>formaPrawna</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dataRejestracji</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>siedziba</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>adres</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>dataRejestracji</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>formaPrawna</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>pkd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>kapitalZakladowy</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nazwa</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>nazwaSkrocona</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>nip</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>numerKRS</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pkd</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>regon</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>reprezentacja</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>siedziba</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ul Bałtycka 126, 85-707 Bydgoszcz</t>
+          <t>0001000380</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2021-03-27</t>
+          <t>5000013809</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300013803</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Vistula Brokers 381 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amber Tech Holding sp. z o.o.</t>
+          <t>Vistula Brokers 381 sp. z o.o.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amber Tech Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5350246948</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8161292135</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>111330107</t>
+          <t>ul Szkolna 71/6, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>50000 PLN</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Bydgoszcz</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 78, 35-001 Rzeszów</t>
+          <t>0001000381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>5000013815</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Nova Markets 382 sp. z o.o.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Group SP Z O O</t>
+          <t>Nova Markets 382 S.A.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Group</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9937151931</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5878379213</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>168226080</t>
+          <t>ulica Lipowa 72/7, 30-302 Kraków</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>55000 PLN</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ul. Konopnickiej 44, 30-302 Kraków</t>
+          <t>0001000382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>5000013821</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300013826</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Meridian Pay 383 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Holding sp z oo</t>
+          <t>Meridian Pay 383 sp. z o.o.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VISTULA DATA HUB HOLDING</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9385028477</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7005355882</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>348118082</t>
+          <t>ul. Słoneczna 73, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>60000 PLN</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Kraków</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20-819 Lublin, Topolowa 49</t>
+          <t>0001000383</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2018-10-12</t>
+          <t>5000013838</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013832</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Helix Invest 384 SP Z OO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nebula Analytics Group SP Z O O</t>
+          <t>Helix Invest 384 sp. z o.o.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nebula Analytics Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0721624742</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1703793061</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>892004582</t>
+          <t>60-126 Poznań, Różana 74 m. 9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>65000 PLN</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>60-126 Poznań, Głogowska 72</t>
+          <t>0001000384</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>5000013844</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013849</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Lumen Finance 385 sp z oo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vistula Data Hub Tech SP Z OO </t>
+          <t>Lumen Finance 385 S.A.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0167599300</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1744205405</t>
+          <t>2020-01-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ul Wiosenna 75/10, 50-101 Wrocław</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>155674092</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>70000 PLN</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40-121 Katowice, ul Chorzowska 149 m.28</t>
+          <t>0001000385</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>5000013850</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300013855</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Sfera Ubezpieczenia 386 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Altair Finance Services Sp. z o.o.</t>
+          <t>Sfera Ubezpieczenia 386 sp. z o.o.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALTAIR FINANCE SERVICES</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5081595904</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7601380795</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>118121652</t>
+          <t>ulica Topolowa 76/11, 20-819 Lublin</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>75000 PLN</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Katowice</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 48/25, 10-687 Olsztyn</t>
+          <t>0001000386</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>5000013867</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300013861</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Atlas Data 387 sp. z o.o.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Polska spółka akcyjna</t>
+          <t>Atlas Data 387 sp. z o.o.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Balitc Med Supply Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9465846392</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7244792975</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>914489400</t>
+          <t>ul. Bałtycka 77, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>80000 PLN</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Olsztyn</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ul Jarzębinowa 94, 10-687 Olsztyn</t>
+          <t>0001000387</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>5000013873</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013878</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Pomerania Trade 388 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Altair Finance Group SP Z O O</t>
+          <t>Pomerania Trade 388 S.A.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALTAIR FINANCE GROUP</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6704477714</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3176970856</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>759105639</t>
+          <t>10-687 Olsztyn, Jarzębinowa 78 m. 13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>85000 PLN</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ulica Jarzębinowa 3/6, 10-687 Olsztyn</t>
+          <t>0001000388</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>5000013888</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013884</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Mazovia Asset 389 SP Z OO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polaris Medical Tech SP Z O O</t>
+          <t>Mazovia Asset 389 sp. z o.o.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polaris Medical Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9802764482</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2769588708</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ul Srebrna 79/14, 81-350 Gdynia</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>62.01.Z</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>942660366</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>90000 PLN</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ul Konopnickiej 157, 30-302 Kraków</t>
+          <t>0001000389</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>5000013896</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300013890</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Kurs Solutions 390 sp z oo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nebul aAnalytics Services sp. z o.o.</t>
+          <t>Kurs Solutions 390 sp. z o.o.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nebula Analytics Services</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9249418016</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3070081334</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>902374326</t>
+          <t>ulica Portowa 80/15, 90-001 Łódź</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>95000 PLN</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 124, 10-687 Olsztyn</t>
+          <t>0001000390</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>5000013904</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300013909</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Nebula Analytics 391 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Altair Finance Group Sp. z o.o.</t>
+          <t>Nebula Analytics 391 S.A.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALTAIR FINANCE GROUP</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1625055326</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6377348503</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ul. Głogowska 81, 00-810 Warszawa</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>027721793</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100000 PLN</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Olsztyn</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 20/2, 10-687 Olsztyn</t>
+          <t>0001000391</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>5000013910</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300013915</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Baltic Med Supply 392 sp. z o.o.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Polsk aSp. z o.o.</t>
+          <t>Baltic Med Supply 392 sp. z o.o.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4963550193</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1071912943</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>370265781</t>
+          <t>30-302 Kraków, Królewska 82 m. 17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>105000 PLN</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 44, 35-001 Rzeszów</t>
+          <t>0001000392</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>5000013927</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300013921</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Orbis Retail Solutions 393 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sloutions sp. z o.o.</t>
+          <t>Orbis Retail Solutions 393 sp. z o.o.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Solutions</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3580471180</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2400613865</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>496602514</t>
+          <t>ul Piękna 83/18, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>110000 PLN</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ulica Konopnickiej 13/9, 30-302 Kraków</t>
+          <t>0001000393</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2019-10-16</t>
+          <t>5000013933</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300013938</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Finex Capital 394 SP Z OO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hleix Retail Holding Sp. z o.o.</t>
+          <t>Finex Capital 394 S.A.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helix Retail Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1827711488</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7504224640</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ulica Leśna 84/19, 60-126 Poznań</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>694861754</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>115000 PLN</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ulica Topolowa 77/9, 20-819 Lublin</t>
+          <t>0001000394</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>5000013944</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S.A.</t>
+          <t>300013944</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Aster Payments 395 sp z oo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Solutions S.A.</t>
+          <t>Aster Payments 395 sp. z o.o.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Solutions</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4970424169</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2670880501</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>513786268</t>
+          <t>ul. Polna 85, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>120000 PLN</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Lublin</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>50-101 Wrocław, ul Kazimierza Wielkiego 90 m.4</t>
+          <t>0001000395</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>5000013956</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300013950</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Vistula Brokers 396 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helix Retail Polska sp z oo</t>
+          <t>Vistula Brokers 396 sp. z o.o.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HELIX RETAIL POLSKA</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2192283491</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7842845576</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>186770667</t>
+          <t>20-819 Lublin, Szkolna 86 m. 21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>125000 PLN</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00-810 Warszawa, ul Srebrna 144 m.5</t>
+          <t>0001000396</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>5000013962</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>300013967</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nova Markets 397 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nova Markets 397 S.A.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>spółka akcyjna</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>100000 PLN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Vistula Data Hub Services spółka akcyjna</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vistula Data Hub Services</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6166296586</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1620637035</t>
+          <t>2020-01-19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>595915167</t>
+          <t>ul Lipowa 87/22, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>130000 PLN</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Warszawa</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00-810 Warszawa, ul Srebrna 100 m.1</t>
+          <t>0001000397</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>5000013979</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300013973</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Meridian Pay 398 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amber Tech Services ps z oo</t>
+          <t>Meridian Pay 398 sp. z o.o.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amber Tech Services</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9300460356</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3871834100</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>066584843</t>
+          <t>ulica Słoneczna 88/23, 10-687 Olsztyn</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>135000 PLN</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Warszawa</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>40-121 Katowice, ul Chorzowska 131 m.18</t>
+          <t>0001000398</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>5000013985</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>300013980</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Helix Invest 399 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Helix Invest 399 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>50000 PLN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Altair Finance Group spółka z ograniczoną odpwoiedzialnością</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Altair Finance Group</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5501352471</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6282850725</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>532052851</t>
+          <t>ul. Różana 89, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>140000 PLN</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30-302 Kraków, ul Konopnickiej 144 m.30</t>
+          <t>0001000399</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>5000013991</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300013996</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Lumen Finance 400 sp z oo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Amber Tech Holding SP Z O O</t>
+          <t>Lumen Finance 400 S.A.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Abmer Tech Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1241373949</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7930925239</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>060563607</t>
+          <t>90-001 Łódź, Wiosenna 90 m. 25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>145000 PLN</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ul Srebrna 33, 00-810 Warszawa</t>
+          <t>0001000400</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>5000014000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300014004</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Sfera Ubezpieczenia 401 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Altair Finance Group spółka akcyjna</t>
+          <t>Sfera Ubezpieczenia 401 sp. z o.o.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Altair Finance Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4386668470</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3388319602</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>509270400</t>
+          <t>ul Topolowa 91/1, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>50000 PLN</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ul. Chorzowska 38, 40-121 Katowice</t>
+          <t>0001000401</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>5000014016</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>300014010</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Atlas Data 402 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Atlas Data 402 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1200000 PLN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Nebula Analytics Solutions spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Nebula Analytisc Solutions</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3678281689</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9982477075</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>186210986</t>
+          <t>ulica Bałtycka 92/2, 30-302 Kraków</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>55000 PLN</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Katowice</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ul. Srebrna 159/28, 00-810 Warszawa</t>
+          <t>0001000402</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>5000014022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014027</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Pomerania Trade 403 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech SP Z O O</t>
+          <t>Pomerania Trade 403 S.A.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3180666405</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7890483346</t>
+          <t>2020-07-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>586726021</t>
+          <t>ul. Jarzębinowa 93, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>60000 PLN</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40-121 Katowice, Chorzowska 136</t>
+          <t>0001000403</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>5000014039</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014033</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Mazovia Asset 404 SP Z OO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Altair Finance Polska Sp. z o.o.</t>
+          <t>Mazovia Asset 404 sp. z o.o.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Altair Finance Polsak</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4331782730</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7813731421</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>756247994</t>
+          <t>60-126 Poznań, Srebrna 94 m. 4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>65000 PLN</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, ul Bałtycka 147 m.15</t>
+          <t>0001000404</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2020-07-05</t>
+          <t>5000014045</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S.A.</t>
+          <t>300014040</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Kurs Solutions 405 sp z oo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Group S.A.</t>
+          <t>Kurs Solutions 405 sp. z o.o.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3392389862</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7940601541</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>382738688</t>
+          <t>ul Portowa 95/5, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>70000 PLN</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ul. Konopnickiej 20, 30-302 Kraków</t>
+          <t>0001000405</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2022-01-21</t>
+          <t>5000014051</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>300014056</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 406 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 406 S.A.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>spółka akcyjna</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>5000 PLN</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Nebula Analytics Solutions spółka akcyjna</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Nebula Analytics Solutions</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6274205225</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0091665954</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>543001784</t>
+          <t>ulica Głogowska 96/6, 20-819 Lublin</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>75000 PLN</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30-302 Kraków, Konopnickiej 87</t>
+          <t>0001000406</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>5000014068</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014062</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Baltic Med Supply 407 sp. z o.o.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech Sp. z o.o.</t>
+          <t>Baltic Med Supply 407 sp. z o.o.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7559875920</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0534774116</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>028595388</t>
+          <t>ul. Królewska 97, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>80000 PLN</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ulica Chorzowska 55/10, 40-121 Katowice</t>
+          <t>0001000407</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2019-01-11</t>
+          <t>5000014074</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014079</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Orbis Retail Solutions 408 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Solutions sp z oo</t>
+          <t>Orbis Retail Solutions 408 sp. z o.o.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Solutions</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4212826585</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7100997844</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>298299316</t>
+          <t>10-687 Olsztyn, Piękna 98 m. 8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>85000 PLN</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Katowice</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ul. Topolowa 167, 20-819 Lublin</t>
+          <t>0001000408</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2018-11-13</t>
+          <t>5000014080</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014085</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Finex Capital 409 SP Z OO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nova Systems Holding Sp. z o.o.</t>
+          <t>Finex Capital 409 S.A.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>oNva Systems Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5907312821</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4070806313</t>
+          <t>2020-01-04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ul Leśna 99/9, 81-350 Gdynia</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>62.01.Z</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>959435784</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>90000 PLN</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ul. Kazimierza Wielkiego 156/9, 50-101 Wrocław</t>
+          <t>0001000409</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>5000014097</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014091</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Aster Payments 410 sp z oo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polaris Medical Polska SP Z O O</t>
+          <t>Aster Payments 410 sp. z o.o.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polaris Medical Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5441983857</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3798775239</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ulica Polna 100/10, 90-001 Łódź</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>62.02.Z</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>996369184</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>95000 PLN</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ul. Kazimierza Wielkiego 26, 50-101 Wrocław</t>
+          <t>0001000410</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>5000014105</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Vistula Brokers 411 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech sp. z o.o.</t>
+          <t>Vistula Brokers 411 sp. z o.o.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1000278649</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1793134756</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>196176502</t>
+          <t>ul. Szkolna 101, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>100000 PLN</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ulica Jarzębinowa 127/13, 10-687 Olsztyn</t>
+          <t>0001000411</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>5000014111</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014116</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Nova Markets 412 sp. z o.o.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amber Tech Group SP Z O O</t>
+          <t>Nova Markets 412 S.A.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AMBER TECH GROUP</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3872075793</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7927462268</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>975311524</t>
+          <t>30-302 Kraków, Lipowa 102 m. 12</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>105000 PLN</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, Bałtycka 127</t>
+          <t>0001000412</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>5000014128</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014122</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Meridian Pay 413 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Holding sp. z o.o.</t>
+          <t>Meridian Pay 413 sp. z o.o.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BALTIC MED SUPPLY HOLDING</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2075914456</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6850705182</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>511031867</t>
+          <t>ul Słoneczna 103/13, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>110000 PLN</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, Bałtycka 62</t>
+          <t>0001000413</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2019-01-14</t>
+          <t>5000014134</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S.A.</t>
+          <t>300014139</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Helix Invest 414 SP Z OO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amber Tech Holding S.A.</t>
+          <t>Helix Invest 414 sp. z o.o.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amber Tech Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0781629309</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2147061653</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>730534289</t>
+          <t>ulica Różana 104/14, 60-126 Poznań</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>115000 PLN</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Bydgoszcz</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35-001 Rzeszów, ul 3 Maja 164 m.16</t>
+          <t>0001000414</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>5000014140</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014145</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Lumen Finance 415 sp z oo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polaris Medical Solutions sp. z o.o.</t>
+          <t>Lumen Finance 415 S.A.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polaris Medical Solutions</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9830878847</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1994670996</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>087496122</t>
+          <t>ul. Wiosenna 105, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>120000 PLN</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ul. Kazimierza Wielkiego 134/9, 50-101 Wrocław</t>
+          <t>0001000415</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2019-12-21</t>
+          <t>5000014157</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014151</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Sfera Ubezpieczenia 416 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nebula Analytics Solutions SP Z O O</t>
+          <t>Sfera Ubezpieczenia 416 sp. z o.o.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NEBULA ANALYTICS SOLUTIONS</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6378131915</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2464913716</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>509423159</t>
+          <t>20-819 Lublin, Topolowa 106 m. 16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>125000 PLN</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ul. Głogowska 79/14, 60-126 Poznań</t>
+          <t>0001000416</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>5000014163</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>300014168</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Atlas Data 417 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Atlas Data 417 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1200000 PLN</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Meridian Trade Tech spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>MERIDIAN TRADE TECH</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4977957240</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7729420670</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>805858240</t>
+          <t>ul Bałtycka 107/17, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>130000 PLN</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ulica Kazimierza Wielkiego 179/2, 50-101 Wrocław</t>
+          <t>0001000417</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>5000014177</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014174</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Pomerania Trade 418 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helix Retail Holding sp. z o.o.</t>
+          <t>Pomerania Trade 418 S.A.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helix Retail Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5576941513</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6823955434</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>482138011</t>
+          <t>ulica Jarzębinowa 108/18, 10-687 Olsztyn</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>135000 PLN</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>60-126 Poznań, Głogowska 177</t>
+          <t>0001000418</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>5000014186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014180</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Mazovia Asset 419 SP Z OO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Tech Sp. z o.o.</t>
+          <t>Mazovia Asset 419 sp. z o.o.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VISTULA DATA HUB TECH</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0625873608</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8294078286</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>255872937</t>
+          <t>ul. Srebrna 109, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>140000 PLN</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ulica Portowa 64/18, 81-350 Gdynia</t>
+          <t>0001000419</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
+          <t>5000014192</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>300014197</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 420 sp z oo</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 420 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>5000 PLN</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Amber Tech Solutions spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Amber Tech Solutions</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2208346442</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2239657537</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>644512562</t>
+          <t>90-001 Łódź, Portowa 110 m. 20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>145000 PLN</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>81-350 Gdynia, ul Portowa 97 m.21</t>
+          <t>0001000420</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
+          <t>5000014200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>spółka z ograniczoną odpowiedzialnością</t>
+          <t>300014205</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Nebula Analytics 421 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meridian Trade Group spółka z ograniczoną odpowiedzialnością</t>
+          <t>Nebula Analytics 421 S.A.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Meridian Trade Group</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0811071492</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9694123528</t>
+          <t>2020-01-16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>889908886</t>
+          <t>ul Głogowska 111/21, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>50000 PLN</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Gdynia</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>50-101 Wrocław, ul Kazimierza Wielkiego 127 m.7</t>
+          <t>0001000421</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>5000014217</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>300014211</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 422 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 422 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1200000 PLN</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Helix Retail Group spółka z ograniczoną odpowiedzilanością</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>HELIX RETAIL GROUP</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1818018747</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9180438430</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>979756842</t>
+          <t>ulica Królewska 112/22, 30-302 Kraków</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>55000 PLN</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30-302 Kraków, Konopnickiej 89</t>
+          <t>0001000422</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2022-01-03</t>
+          <t>5000014223</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300014228</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Orbis Retail Solutions 423 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Polaris Medical Group spółka akcyjna</t>
+          <t>Orbis Retail Solutions 423 sp. z o.o.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Polaris Medical Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2380137020</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8910953100</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ul. Piękna 113, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>62.01.Z</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>179251362</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>60000 PLN</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ulica Portowa 13/19, 81-350 Gdynia</t>
+          <t>0001000423</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2022-04-08</t>
+          <t>5000014233</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014234</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Finex Capital 424 SP Z OO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Helix Retail Polska sp. z o.o.</t>
+          <t>Finex Capital 424 S.A.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HELIX RETAIL POLSKA</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7305151332</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5333501626</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>251049461</t>
+          <t>60-126 Poznań, Leśna 114 m. 24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>65000 PLN</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ulica Srebrna 24/14, 00-810 Warszawa</t>
+          <t>0001000424</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>5000014246</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014240</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Aster Payments 425 sp z oo</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Helix Retail Group Sp. z o.o.</t>
+          <t>Aster Payments 425 sp. z o.o.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Helix Retail Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0232016519</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6500394558</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>464201819</t>
+          <t>ul Polna 115/25, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>70000 PLN</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Warszawa</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ul. Kazimierza Wielkiego 21/27, 50-101 Wrocław</t>
+          <t>0001000425</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>5000014252</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014257</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Vistula Brokers 426 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nova Systems Services Sp. z o.o.</t>
+          <t>Vistula Brokers 426 sp. z o.o.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NOVA SYSTEMS SERVICES</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9550800290</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3476414427</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ulica Szkolna 116/1, 20-819 Lublin</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>62.01.Z</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>197453145</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>75000 PLN</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Wrocław</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ulica Srebrna 166/9, 00-810 Warszawa</t>
+          <t>0001000426</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
+          <t>5000014269</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>spółka z ograniczoną odpowiedzialnością</t>
+          <t>300014263</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Nova Markets 427 sp. z o.o.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Nova Markets 427 S.A.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3417622809</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2360741706</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>022525531</t>
+          <t>ul. Lipowa 117, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>80000 PLN</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ul Kazimierza Wielkiego 97, 50-101 Wrocław</t>
+          <t>0001000427</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>5000014275</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014270</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Meridian Pay 428 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Helix Retail Holding Sp. z o.o.</t>
+          <t>Meridian Pay 428 sp. z o.o.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Helix Retail Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6102855143</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0845014399</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>10-687 Olsztyn, Słoneczna 118 m. 3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>64.19.Z</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>925709928</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>85000 PLN</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Wrocław</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, ul Bałtycka 179 m.3</t>
+          <t>0001000428</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>5000014281</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>300014286</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Helix Invest 429 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Helix Invest 429 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>100000 PLN</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Amber Tech Tech spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AMBER TECH TECH</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3876738431</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5071970957</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>445406914</t>
+          <t>ul Różana 119/4, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>90000 PLN</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ulica Jarzębinowa 126/7, 10-687 Olsztyn</t>
+          <t>0001000429</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>5000014298</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>spółka z ograniczoną odpowiedzialnością</t>
+          <t>300014292</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Lumen Finance 430 sp z oo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Amber Tech Polska spółka z ograniczoną odpowiedzialnością</t>
+          <t>Lumen Finance 430 S.A.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Amber Tech Polska</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6816051917</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5665141343</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>076832987</t>
+          <t>ulica Wiosenna 120/5, 90-001 Łódź</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>95000 PLN</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>50-101 Wrocław, ul Kazimierza Wielkiego 31 m.24</t>
+          <t>0001000430</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>5000014306</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>300014300</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 431 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 431 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1200000 PLN</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Helix Retail Group spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Helix Retail Group</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6473116885</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1476207347</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>873541455</t>
+          <t>ul. Topolowa 121, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>100000 PLN</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Wrocław</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ul Kazimierza Wielkiego 53, 50-101 Wrocław</t>
+          <t>0001000431</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>5000014312</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>300014317</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Atlas Data 432 sp. z o.o.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Meridian Trade Polska SA</t>
+          <t>Atlas Data 432 sp. z o.o.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Meridian Trade Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4503083491</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7363149318</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>137229380</t>
+          <t>30-302 Kraków, Bałtycka 122 m. 7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>105000 PLN</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>50-101 Wrocław, Kazimierza Wielkiego 134</t>
+          <t>0001000432</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>5000014329</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014323</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Pomerania Trade 433 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nebula Analytics Group Sp. z o.o.</t>
+          <t>Pomerania Trade 433 S.A.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nebula Analytics Group</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2883793985</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9072648810</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>503916781</t>
+          <t>ul Jarzębinowa 123/8, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>110000 PLN</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Wrocław</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 45, 10-687 Olsztyn</t>
+          <t>0001000433</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>5000014335</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014330</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Mazovia Asset 434 SP Z OO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Tech SP Z O O</t>
+          <t>Mazovia Asset 434 sp. z o.o.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ORBIS RETAIL SOLUTIONS TECH</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4128044712</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6115623067</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>801946701</t>
+          <t>ulica Srebrna 124/9, 60-126 Poznań</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>115000 PLN</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ul. Konopnickiej 152/21, 30-302 Kraków</t>
+          <t>0001000434</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>5000014341</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014346</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Kurs Solutions 435 sp z oo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nova Systems Services sp. z o.o.</t>
+          <t>Kurs Solutions 435 sp. z o.o.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nova Systems Services</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4583618837</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3756184535</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ul. Portowa 125, 50-101 Wrocław</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>64.19.Z</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>777785929</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>120000 PLN</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00-810 Warszawa, Srebrna 78</t>
+          <t>0001000435</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>5000014358</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014352</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Nebula Analytics 436 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Altair Finance Polska sp z oo</t>
+          <t>Nebula Analytics 436 S.A.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Altair Finance Polska</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9313294027</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9808655108</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>619970783</t>
+          <t>20-819 Lublin, Głogowska 126 m. 11</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>125000 PLN</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ul Portowa 101, 81-350 Gdynia</t>
+          <t>0001000436</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>5000014364</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014369</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Baltic Med Supply 437 sp. z o.o.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Holding SP Z O O</t>
+          <t>Baltic Med Supply 437 sp. z o.o.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2445697918</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4109600661</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>615317660</t>
+          <t>ul Królewska 127/12, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>130000 PLN</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Gdynia</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00-810 Warszawa, Srebrna 50</t>
+          <t>0001000437</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
+          <t>5000014370</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014375</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Orbis Retail Solutions 438 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nova Systems Holding Sp. z o.o.</t>
+          <t>Orbis Retail Solutions 438 sp. z o.o.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nova Systems Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1213455799</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5126193790</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>229309443</t>
+          <t>ulica Piękna 128/13, 10-687 Olsztyn</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>135000 PLN</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Warszawa</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ul. Topolowa 151, 20-819 Lublin</t>
+          <t>0001000438</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>5000014387</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014381</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Finex Capital 439 SP Z OO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Holding SP Z O O</t>
+          <t>Finex Capital 439 S.A.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vistula Data Hub Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7694136674</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1209454028</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>944388269</t>
+          <t>ul. Leśna 129, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>140000 PLN</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 74/22, 35-001 Rzeszów</t>
+          <t>0001000439</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>5000014393</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014398</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Aster Payments 440 sp z oo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Altair Finance Holding Sp. z o.o.</t>
+          <t>Aster Payments 440 sp. z o.o.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ALTAIR FINANCE HOLDING</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2874075193</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2707254452</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>90-001 Łódź, Polna 130 m. 15</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>64.19.Z</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>786109547</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>145000 PLN</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Rzeszów</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ul. Kazimierza Wielkiego 124, 50-101 Wrocław</t>
+          <t>0001000440</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>5000014401</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014406</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Vistula Brokers 441 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Meridian Trade Group sp z oo</t>
+          <t>Vistula Brokers 441 sp. z o.o.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Meridian Trade Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8640946654</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8616338638</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>130326249</t>
+          <t>ul Szkolna 131/16, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>46.46.Z</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>50000 PLN</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30-302 Kraków, Konopnickiej 159</t>
+          <t>0001000441</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2018-02-18</t>
+          <t>5000014418</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>300014412</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Nova Markets 442 sp. z o.o.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska SA</t>
+          <t>Nova Markets 442 S.A.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NEBULA ANALYTICS POLSKA</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6127793333</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2331524041</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>575842768</t>
+          <t>ulica Lipowa 132/17, 30-302 Kraków</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>55000 PLN</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ul Topolowa 137, 20-819 Lublin</t>
+          <t>0001000442</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
+          <t>5000014424</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014429</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Meridian Pay 443 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polaris Medical Group sp z oo</t>
+          <t>Meridian Pay 443 sp. z o.o.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polaris Medical Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4401989289</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5234655461</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ul. Słoneczna 133, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>203846726</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>60000 PLN</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ulica Głogowska 107/3, 60-126 Poznań</t>
+          <t>0001000443</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>5000014430</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>300014435</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Helix Invest 444 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Helix Invest 444 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>10000 PLN</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Orbis Retail Solutions Polska spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Orbis Retali Solutions Polska</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4394428054</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6119597372</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>530315846</t>
+          <t>60-126 Poznań, Różana 134 m. 19</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>65000 PLN</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 63/25, 35-001 Rzeszów</t>
+          <t>0001000444</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>5000014447</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SP Z O O</t>
+          <t>300014441</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Lumen Finance 445 sp z oo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Altair Finance Group SP Z O O</t>
+          <t>Lumen Finance 445 S.A.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Altair Finance Group</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9783018986</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5188857878</t>
+          <t>2020-01-13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>280957283</t>
+          <t>ul Wiosenna 135/20, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>70000 PLN</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>40-121 Katowice, ul Chorzowska 164 m.12</t>
+          <t>0001000445</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>5000014453</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300014458</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Sfera Ubezpieczenia 446 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Helix Retail Services spółka akcyjna</t>
+          <t>Sfera Ubezpieczenia 446 sp. z o.o.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helix Retail Services</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4847739202</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9802075204</t>
+          <t>2021-02-14</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>690743906</t>
+          <t>ulica Topolowa 136/21, 20-819 Lublin</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>75000 PLN</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ul Srebrna 140, 00-810 Warszawa</t>
+          <t>0001000446</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>5000014466</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>300014464</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Atlas Data 447 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Atlas Data 447 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>1200000 PLN</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Nova Sytsems Polska spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nova Systems Polska</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8604283167</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6183215290</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>074166430</t>
+          <t>ul. Bałtycka 137, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>80000 PLN</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Warszawa</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>60-126 Poznań, ul Głogowska 120 m.22</t>
+          <t>0001000447</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>5000014476</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014470</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Pomerania Trade 448 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech Sp. z o.o.</t>
+          <t>Pomerania Trade 448 S.A.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Meridian Trade Tech</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>9378486523</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7579033675</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>947910999</t>
+          <t>10-687 Olsztyn, Jarzębinowa 138 m. 23</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>85000 PLN</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 158, 10-687 Olsztyn</t>
+          <t>0001000448</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>5000014482</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014487</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Mazovia Asset 449 SP Z OO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Altai rFinance Tech sp z oo</t>
+          <t>Mazovia Asset 449 sp. z o.o.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Altair Finance Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3080480886</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3825117230</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>358217263</t>
+          <t>ul Srebrna 139/24, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>64.19.Z</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>90000 PLN</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ulica Chorzowska 25/28, 40-121 Katowice</t>
+          <t>0001000449</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>5000014499</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300014493</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Kurs Solutions 450 sp z oo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Polaris Medical Services spółka akcyjna</t>
+          <t>Kurs Solutions 450 sp. z o.o.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Polaris Medical Services</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4641473594</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5215267371</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>107068686</t>
+          <t>ulica Portowa 140/25, 90-001 Łódź</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>95000 PLN</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ul Jarzębinowa 37, 10-687 Olsztyn</t>
+          <t>0001000450</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>5000014507</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>300014501</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 451 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 451 S.A.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>spółka akcyjna</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>50000 PLN</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Altair Finance Srevices spółka akcyjna</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>ALTAIR FINANCE SERVICES</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8815660309</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5961159533</t>
+          <t>2020-07-19</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>841629062</t>
+          <t>ul. Głogowska 141, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>100000 PLN</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>60-126 Poznań, Głogowska 134</t>
+          <t>0001000451</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>5000014513</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>spółka akcyjna</t>
+          <t>300014518</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Baltic Med Supply 452 sp. z o.o.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amber Tech Tech spółka akcyjna</t>
+          <t>Baltic Med Supply 452 sp. z o.o.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Amber Tech Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3125812876</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>9516289084</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30-302 Kraków, Królewska 142 m. 2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>62.01.Z</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>548262773</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>105000 PLN</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>50-101 Wrocław, Kazimierza Wielkiego 95</t>
+          <t>0001000452</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>5000014522</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014524</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Orbis Retail Solutions 453 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Group sp. z o.o.</t>
+          <t>Orbis Retail Solutions 453 sp. z o.o.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BALTIC MED SUPPLY GROUP</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8784138312</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8454705005</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ul Piękna 143/3, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>745807664</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>110000 PLN</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Wrocław</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ul Topolowa 162, 20-819 Lublin</t>
+          <t>0001000453</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>5000014536</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>300014530</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Finex Capital 454 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Finex Capital 454 S.A.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>spółka akcyjna</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>10000 PLN</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Amber Tech Solutions spółka akcyjna</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Amber Tech Solutions</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3909174479</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5844801277</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>63.11.Z</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>127715685</t>
+          <t>ulica Leśna 144/4, 60-126 Poznań</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>115000 PLN</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, ul Bałtycka 178 m.15</t>
+          <t>0001000454</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>5000014542</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014547</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Aster Payments 455 sp z oo</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Meridian Trade Holding sp z oo</t>
+          <t>Aster Payments 455 sp. z o.o.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Meridian Trade Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>9801888003</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5872802386</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>562600805</t>
+          <t>ul. Polna 145, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>120000 PLN</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ulica Bałtycka 117/20, 85-707 Bydgoszcz</t>
+          <t>0001000455</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
+          <t>5000014559</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014553</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Vistula Brokers 456 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Tech sp. z o.o.</t>
+          <t>Vistula Brokers 456 sp. z o.o.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions eTch</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9109233558</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8635834926</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>20-819 Lublin, Szkolna 146 m. 6</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>389874955</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>125000 PLN</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ul. Topolowa 71, 20-819 Lublin</t>
+          <t>0001000456</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>5000014565</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>spółka z ograniczoną odpowiedzialnością</t>
+          <t>300014560</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1200000 PLN</t>
+          <t>Nova Markets 457 sp. z o.o.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Altair Finance Solutions spółka z ograniczoną odpowiedzialnością</t>
+          <t>Nova Markets 457 S.A.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Altair Finance Solutions</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>6288658072</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8917284584</t>
+          <t>2020-01-25</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>874940092</t>
+          <t>ul Lipowa 147/7, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>130000 PLN</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
           <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Lublin</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ul Portowa 163, 81-350 Gdynia</t>
+          <t>0001000457</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2018-01-23</t>
+          <t>5000014571</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014576</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Meridian Pay 458 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nebula Analytics Tech Sp. z o.o.</t>
+          <t>Meridian Pay 458 sp. z o.o.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nebula Analytics Tech</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0251906724</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6900158123</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>624249470</t>
+          <t>ulica Słoneczna 148/8, 10-687 Olsztyn</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>135000 PLN</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35-001 Rzeszów, ul 3 Maja 123 m.15</t>
+          <t>0001000458</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>5000014588</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S.A.</t>
+          <t>300014582</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Helix Invest 459 SP Z OO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nova Systems Group S.A.</t>
+          <t>Helix Invest 459 sp. z o.o.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nova Systems Group</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0664878264</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8287657555</t>
+          <t>2022-03-27</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>258685685</t>
+          <t>ul. Różana 149, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>140000 PLN</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>40-121 Katowice, Chorzowska 74</t>
+          <t>0001000459</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>5000014594</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>300014599</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Lumen Finance 460 sp z oo</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nebula Aanlytics Holding SA</t>
+          <t>Lumen Finance 460 S.A.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nebula Analytics Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3875955942</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4505633706</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>951181961</t>
+          <t>90-001 Łódź, Wiosenna 150 m. 10</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>145000 PLN</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>40-121 Katowice, Chorzowska 150</t>
+          <t>0001000460</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>5000014602</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>300014607</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 461 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 461 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>10000 PLN</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Helix Retail Services spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Helix Retail Services</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0053126055</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8776458084</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>319652179</t>
+          <t>ul Topolowa 151/11, 00-810 Warszawa</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>likwidator samodzielnie</t>
+          <t>66.12.Z</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>50000 PLN</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>każdy członek zarządu samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ul Głogowska 89, 60-126 Poznań</t>
+          <t>0001000461</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>5000014619</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>S.A.</t>
+          <t>300014613</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Atlas Data 462 sp. z o.o.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Polaris Medical Polska S.A.</t>
+          <t>Atlas Data 462 sp. z o.o.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Polaris Medical Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4028106076</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2743514928</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>64.19.Z</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>632702317</t>
+          <t>ulica Bałtycka 152/12, 30-302 Kraków</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>55000 PLN</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ul. Głogowska 138, 60-126 Poznań</t>
+          <t>0001000462</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>5000014625</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014620</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Pomerania Trade 463 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Meridian Trade Polska sp. z o.o.</t>
+          <t>Pomerania Trade 463 S.A.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MERIDIAN TRADE POLSKA</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4589275234</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3547224055</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>62.02.Z</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>306113900</t>
+          <t>ul. Jarzębinowa 153, 80-241 Gdańsk</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>60000 PLN</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
           <t>likwidator samodzielnie</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Poznań</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ul 3 Maja 173, 35-001 Rzeszów</t>
+          <t>0001000463</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>5000014631</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014636</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Mazovia Asset 464 SP Z OO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Altair Fiannce Holding Sp. z o.o.</t>
+          <t>Mazovia Asset 464 sp. z o.o.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Altair Finance Holding</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7223242043</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0175056655</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>60-126 Poznań, Srebrna 154 m. 14</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>46.46.Z</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>899065869</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>dwóch członków zarządu łącznie</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>65000 PLN</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>85-707 Bydgoszcz, Bałtycka 180</t>
+          <t>0001000464</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>5000014648</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014642</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Kurs Solutions 465 sp z oo</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska sp z oo</t>
+          <t>Kurs Solutions 465 sp. z o.o.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6176294846</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8928243509</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>791353295</t>
+          <t>ul Portowa 155/15, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>każdy członek zarządu samodzielnie</t>
+          <t>62.01.Z</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>70000 PLN</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>W TRAKCIE LIKWIDACJI</t>
+          <t>dwóch członków zarządu łącznie</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ul. Jarzębinowa 97, 10-687 Olsztyn</t>
+          <t>0001000465</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2018-12-22</t>
+          <t>5000014654</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>300014659</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>50000 PLN</t>
+          <t>Nebula Analytics 466 spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polaris Medical Group SA</t>
+          <t>Nebula Analytics 466 S.A.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Polaris Medical Group</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7382438214</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5672617362</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ulica Głogowska 156/16, 20-819 Lublin</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>924598977</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>75000 PLN</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>40-121 Katowice, ul Chorzowska 171 m.19</t>
+          <t>0001000466</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>5000014660</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014665</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>100000 PLN</t>
+          <t>Baltic Med Supply 467 sp. z o.o.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nova Systems Solutions Sp. z o.o.</t>
+          <t>Baltic Med Supply 467 sp. z o.o.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nova Systems Solutions</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>9591905309</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0462933741</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>62.01.Z</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>535833878</t>
+          <t>ul. Królewska 157, 85-707 Bydgoszcz</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>dwóch członków zarządu łącznie</t>
+          <t>47.91.Z</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>80000 PLN</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>AKTYWNY</t>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ulica Portowa 11/25, 81-350 Gdynia</t>
+          <t>0001000467</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>5000014677</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sp. z o.o.</t>
+          <t>300014671</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Orbis Retail Solutions 468 Sp. z o.o.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Meridian Trade Solutions sp. z o.o.</t>
+          <t>Orbis Retail Solutions 468 sp. z o.o.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Meridian Trade Solutions</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7680940596</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>7025254110</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>47.91.Z</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>556241266</t>
+          <t>10-687 Olsztyn, Piękna 158 m. 18</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>85000 PLN</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Gdynia</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10-687 Olsztyn, ul Jarzębinowa 20 m.6</t>
+          <t>0001000468</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>5000014683</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sp z oo</t>
+          <t>300014688</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5000 PLN</t>
+          <t>Finex Capital 469 SP Z OO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Holding sp z oo</t>
+          <t>Finex Capital 469 S.A.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Holding</t>
+          <t>spółka akcyjna</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0781010124</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4974787067</t>
+          <t>2020-01-10</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>46.46.Z</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>644286307</t>
+          <t>ul Leśna 159/19, 81-350 Gdynia</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>90000 PLN</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
           <t>każdy członek zarządu samodzielnie</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Olsztyn</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ul. Srebrna 113, 00-810 Warszawa</t>
+          <t>0001000469</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2018-11-05</t>
+          <t>5000014699</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sp. z o.o.</t>
+          <t>300014694</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10000 PLN</t>
+          <t>Aster Payments 470 sp z oo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nova Systems Tech Sp. z o.o.</t>
+          <t>Aster Payments 470 sp. z o.o.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NOVA SYSTEMS TECH</t>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3105503158</t>
+          <t>W TRAKCIE LIKWIDACJI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9204993064</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ulica Polna 160/20, 90-001 Łódź</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>47.91.Z</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>041210704</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>95000 PLN</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0001000470</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5000014708</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>300014702</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Vistula Brokers 471 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Vistula Brokers 471 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ul. Szkolna 161, 00-810 Warszawa</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>100000 PLN</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0001000471</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5000014714</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>300014719</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Nova Markets 472 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Nova Markets 472 S.A.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>30-302 Kraków, Lipowa 162 m. 22</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>105000 PLN</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0001000472</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5000014720</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>300014725</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Meridian Pay 473 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Meridian Pay 473 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ul Słoneczna 163/23, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>110000 PLN</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>likwidator samodzielnie</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0001000473</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5000014737</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>300014731</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Helix Invest 474 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Helix Invest 474 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ulica Różana 164/24, 60-126 Poznań</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>115000 PLN</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0001000474</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5000014743</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>300014748</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lumen Finance 475 sp z oo</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Lumen Finance 475 S.A.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ul. Wiosenna 165, 50-101 Wrocław</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>120000 PLN</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>likwidator samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0001000475</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5000014755</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>300014754</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 476 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 476 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>20-819 Lublin, Topolowa 166 m. 1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>125000 PLN</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0001000476</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5000014766</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>300014760</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Atlas Data 477 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Atlas Data 477 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ul Bałtycka 167/2, 85-707 Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>130000 PLN</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0001000477</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5000014772</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>300014777</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Pomerania Trade 478 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Pomerania Trade 478 S.A.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ulica Jarzębinowa 168/3, 10-687 Olsztyn</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>135000 PLN</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>likwidator samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0001000478</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5000014789</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>300014783</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Mazovia Asset 479 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Mazovia Asset 479 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ul. Srebrna 169, 81-350 Gdynia</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>140000 PLN</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0001000479</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5000014795</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>300014790</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 480 sp z oo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 480 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>90-001 Łódź, Portowa 170 m. 5</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>145000 PLN</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0001000480</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5000014803</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>300014808</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 481 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 481 S.A.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2020-01-22</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>Warszawa</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>AKTYWNY</t>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>ul Głogowska 171/6, 00-810 Warszawa</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>50000 PLN</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0001000481</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5000014811</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>300014814</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 482 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 482 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2021-02-23</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>ulica Królewska 172/7, 30-302 Kraków</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>55000 PLN</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0001000482</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5000014826</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>300014820</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Orbis Retail Solutions 483 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Orbis Retail Solutions 483 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>ul. Piękna 173, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>60000 PLN</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0001000483</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5000014832</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>300014837</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Finex Capital 484 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Finex Capital 484 S.A.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>60-126 Poznań, Leśna 174 m. 9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>65000 PLN</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0001000484</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5000014849</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>300014843</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Aster Payments 485 sp z oo</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aster Payments 485 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>ul Polna 175/10, 50-101 Wrocław</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>70000 PLN</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0001000485</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5000014855</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>300014850</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Vistula Brokers 486 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Vistula Brokers 486 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>W TRAKCIE LIKWIDACJI</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>ulica Szkolna 176/11, 20-819 Lublin</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>75000 PLN</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0001000486</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5000014861</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>300014866</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nova Markets 487 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Nova Markets 487 S.A.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>ul. Lipowa 177, 85-707 Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>64.19.Z</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>80000 PLN</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0001000487</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5000014878</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>300014872</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Meridian Pay 488 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Meridian Pay 488 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>10-687 Olsztyn, Słoneczna 178 m. 13</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>85000 PLN</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0001000488</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5000014884</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>300014889</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Helix Invest 489 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Helix Invest 489 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>ul Różana 179/14, 81-350 Gdynia</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>90000 PLN</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0001000489</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5000014890</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>300014895</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lumen Finance 490 sp z oo</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Lumen Finance 490 S.A.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>ulica Wiosenna 180/15, 90-001 Łódź</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>95000 PLN</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0001000490</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5000014909</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>300014903</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 491 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sfera Ubezpieczenia 491 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>ul. Topolowa 1, 00-810 Warszawa</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>100000 PLN</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0001000491</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5000014915</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>300014910</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Atlas Data 492 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Atlas Data 492 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>30-302 Kraków, Bałtycka 2 m. 17</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>105000 PLN</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0001000492</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5000014921</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>300014926</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Pomerania Trade 493 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pomerania Trade 493 S.A.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2020-01-07</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Gdańsk</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>ul Jarzębinowa 3/18, 80-241 Gdańsk</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>110000 PLN</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0001000493</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5000014938</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>300014932</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Mazovia Asset 494 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Mazovia Asset 494 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2021-02-08</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>ulica Srebrna 4/19, 60-126 Poznań</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>46.46.Z</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>115000 PLN</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0001000494</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5000014944</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>300014949</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 495 sp z oo</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kurs Solutions 495 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2022-03-09</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>ul. Portowa 5, 50-101 Wrocław</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>120000 PLN</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0001000495</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5000014950</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>300014955</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 496 spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Nebula Analytics 496 S.A.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Lublin</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>20-819 Lublin, Głogowska 6 m. 21</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>125000 PLN</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>likwidator samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0001000496</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5000014967</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>300014961</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 497 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Baltic Med Supply 497 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>ul Królewska 7/22, 85-707 Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>66.12.Z</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>130000 PLN</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>dwóch członków zarządu łącznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0001000497</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5000014973</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>300014978</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Orbis Retail Solutions 498 Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Orbis Retail Solutions 498 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>ulica Piękna 8/23, 10-687 Olsztyn</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>62.01.Z</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>135000 PLN</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>likwidator samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0001000498</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5000014988</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>300014984</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Finex Capital 499 SP Z OO</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Finex Capital 499 S.A.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>spółka akcyjna</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2020-07-13</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>ul. Leśna 9, 81-350 Gdynia</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>47.91.Z</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>140000 PLN</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>każdy członek zarządu samodzielnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0001000499</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5000014996</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>300014990</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Aster Payments 500 sp z oo</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aster Payments 500 sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Łódź</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>90-001 Łódź, Polna 10 m. 25</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>62.02.Z</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>145000 PLN</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>likwidator samodzielnie</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>